--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -2059,7 +2059,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>
